--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Redbd82e44265420c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R503f314357ac4339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7fd7b75d8f874dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R60caf1c84f284d98"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7fd7b75d8f874dc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R60caf1c84f284d98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R461ca83534f44965"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Ra690d20c5d294bc4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R461ca83534f44965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Ra690d20c5d294bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbee25b8b86c84d65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rca710df678c348f7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbee25b8b86c84d65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rca710df678c348f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R14331bb991d14b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R0da1c5b8945c4c3b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R14331bb991d14b3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R0da1c5b8945c4c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52c463a535964659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R3b961cbdb0ec4e5a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52c463a535964659"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R3b961cbdb0ec4e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99e694f1b507437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Raf0b0a04d51046de"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99e694f1b507437a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Raf0b0a04d51046de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a520c76f6fe4288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R5c6444773d054d24"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a520c76f6fe4288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R5c6444773d054d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec74999324444261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R811423ab97e94bac"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec74999324444261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R811423ab97e94bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R987e56cfa69d4397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R9fa8347c2ddd49dc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R987e56cfa69d4397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R9fa8347c2ddd49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R129efeca136e4053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R46079fd714c04012"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R129efeca136e4053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R46079fd714c04012"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R44c6900118c04426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R9cd174d369eb499e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R44c6900118c04426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R9cd174d369eb499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a020187d4cc476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R1494ab82a7114dbe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a020187d4cc476b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R1494ab82a7114dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0c8e8c9d6154933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R2b7fff51dd1643fa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0c8e8c9d6154933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R2b7fff51dd1643fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb01f02967ffa45b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rf35d1110a90e4568"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb01f02967ffa45b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rf35d1110a90e4568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7310940bc644b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb005f90675c94ed7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_Internal/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7310940bc644b31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rb005f90675c94ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd0f205472b014f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="R02beacd9bac04f12"/>
   </x:sheets>
 </x:workbook>
 </file>
